--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.02972873680424863</v>
       </c>
       <c r="C2" t="n">
-        <v>55914948</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>55914948</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>38415410</v>
+        <v>3770961</v>
       </c>
       <c r="L2" t="n">
-        <v>21662040</v>
+        <v>1854279</v>
       </c>
       <c r="M2" t="n">
-        <v>5488348</v>
+        <v>412992</v>
       </c>
       <c r="N2" t="n">
-        <v>305847</v>
+        <v>16686</v>
       </c>
       <c r="O2" t="n">
-        <v>3298210</v>
+        <v>262498</v>
       </c>
       <c r="P2" t="n">
-        <v>1358554</v>
+        <v>115567</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999042749404907</v>
+        <v>0.9997994899749756</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8669717311859131</v>
+        <v>0.7658770084381104</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7460471987724304</v>
+        <v>0.5747827291488647</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6529955863952637</v>
+        <v>0.4423432350158691</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4732129573822021</v>
+        <v>0.2334947288036346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7208055257797241</v>
+        <v>0.5165280103683472</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7804431319236755</v>
+        <v>0.5978356003761292</v>
       </c>
       <c r="X2" t="n">
-        <v>55914948</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>55914948</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>37306209</v>
+        <v>3700628</v>
       </c>
       <c r="AG2" t="n">
-        <v>20122846</v>
+        <v>1766147</v>
       </c>
       <c r="AH2" t="n">
-        <v>4951883</v>
+        <v>384662</v>
       </c>
       <c r="AI2" t="n">
-        <v>272312</v>
+        <v>15609</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3034517</v>
+        <v>245099</v>
       </c>
       <c r="AK2" t="n">
-        <v>1274212</v>
+        <v>108400</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8394804000854492</v>
+        <v>0.7494581341743469</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6978186964988708</v>
+        <v>0.5512169003486633</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5941091179847717</v>
+        <v>0.4153532981872559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3423576951026917</v>
+        <v>0.1766163557767868</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6636470556259155</v>
+        <v>0.4824270606040955</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7325722575187683</v>
+        <v>0.560893714427948</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.008113317411548419</v>
       </c>
       <c r="C3" t="n">
-        <v>1815</v>
+        <v>486</v>
       </c>
       <c r="D3" t="n">
-        <v>38415410</v>
+        <v>3770961</v>
       </c>
       <c r="E3" t="n">
-        <v>5220452</v>
+        <v>980090</v>
       </c>
       <c r="F3" t="n">
-        <v>325074</v>
+        <v>76484</v>
       </c>
       <c r="G3" t="n">
-        <v>47515</v>
+        <v>8619</v>
       </c>
       <c r="H3" t="n">
-        <v>17865</v>
+        <v>6385</v>
       </c>
       <c r="I3" t="n">
-        <v>2894</v>
+        <v>1022</v>
       </c>
       <c r="J3" t="n">
-        <v>88713299</v>
+        <v>9856382</v>
       </c>
       <c r="K3" t="n">
-        <v>94708110</v>
+        <v>10073598</v>
       </c>
       <c r="L3" t="n">
-        <v>108086630</v>
+        <v>11417086</v>
       </c>
       <c r="M3" t="n">
-        <v>133329145</v>
+        <v>14611751</v>
       </c>
       <c r="N3" t="n">
-        <v>143493848</v>
+        <v>15926355</v>
       </c>
       <c r="O3" t="n">
-        <v>138769726</v>
+        <v>15313611</v>
       </c>
       <c r="P3" t="n">
-        <v>142510599</v>
+        <v>15798972</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8724623322486877</v>
+        <v>0.7784732580184937</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7425307035446167</v>
+        <v>0.5650634765625</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6543153524398804</v>
+        <v>0.4402923285961151</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3826536238193512</v>
+        <v>0.1869181841611862</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7191351652145386</v>
+        <v>0.5136042833328247</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7804157733917236</v>
+        <v>0.5966719388961792</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>37306209</v>
+        <v>3700628</v>
       </c>
       <c r="Z3" t="n">
-        <v>6184375</v>
+        <v>1030061</v>
       </c>
       <c r="AA3" t="n">
-        <v>380443</v>
+        <v>84017</v>
       </c>
       <c r="AB3" t="n">
-        <v>129683</v>
+        <v>18987</v>
       </c>
       <c r="AC3" t="n">
-        <v>26341</v>
+        <v>8837</v>
       </c>
       <c r="AD3" t="n">
-        <v>3974</v>
+        <v>1517</v>
       </c>
       <c r="AE3" t="n">
-        <v>88718652</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>93469142</v>
+        <v>9989243</v>
       </c>
       <c r="AG3" t="n">
-        <v>106746404</v>
+        <v>11350919</v>
       </c>
       <c r="AH3" t="n">
-        <v>132862586</v>
+        <v>14590959</v>
       </c>
       <c r="AI3" t="n">
-        <v>143311231</v>
+        <v>15908362</v>
       </c>
       <c r="AJ3" t="n">
-        <v>138509275</v>
+        <v>15296355</v>
       </c>
       <c r="AK3" t="n">
-        <v>142427637</v>
+        <v>15791851</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8472709655761719</v>
+        <v>0.7639538049697876</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6897702217102051</v>
+        <v>0.5382065773010254</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5903584957122803</v>
+        <v>0.4100896120071411</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3406970500946045</v>
+        <v>0.1748535335063934</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6616401076316833</v>
+        <v>0.4795613288879395</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7319658398628235</v>
+        <v>0.5596687197685242</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.06952380088628761</v>
       </c>
       <c r="C4" t="n">
-        <v>801</v>
+        <v>206</v>
       </c>
       <c r="D4" t="n">
-        <v>5516930</v>
+        <v>1058782</v>
       </c>
       <c r="E4" t="n">
-        <v>21662040</v>
+        <v>1854279</v>
       </c>
       <c r="F4" t="n">
-        <v>1685112</v>
+        <v>290118</v>
       </c>
       <c r="G4" t="n">
-        <v>70458</v>
+        <v>14101</v>
       </c>
       <c r="H4" t="n">
-        <v>209740</v>
+        <v>55271</v>
       </c>
       <c r="I4" t="n">
-        <v>28178</v>
+        <v>8784</v>
       </c>
       <c r="J4" t="n">
-        <v>5353</v>
+        <v>1246</v>
       </c>
       <c r="K4" t="n">
-        <v>5894465</v>
+        <v>1152755</v>
       </c>
       <c r="L4" t="n">
-        <v>7373711</v>
+        <v>1371773</v>
       </c>
       <c r="M4" t="n">
-        <v>2916530</v>
+        <v>520654</v>
       </c>
       <c r="N4" t="n">
-        <v>340473</v>
+        <v>54776</v>
       </c>
       <c r="O4" t="n">
-        <v>1277518</v>
+        <v>245699</v>
       </c>
       <c r="P4" t="n">
-        <v>382193</v>
+        <v>77742</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999521374702454</v>
+        <v>0.9998997449874878</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8697083592414856</v>
+        <v>0.7721237540245056</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7442848086357117</v>
+        <v>0.5698816776275635</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6536548137664795</v>
+        <v>0.4413153827190399</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4231422543525696</v>
+        <v>0.2076264023780823</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7199693918228149</v>
+        <v>0.5150620341300964</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7804294228553772</v>
+        <v>0.597253143787384</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>6640436</v>
+        <v>1122840</v>
       </c>
       <c r="Z4" t="n">
-        <v>20122846</v>
+        <v>1766147</v>
       </c>
       <c r="AA4" t="n">
-        <v>1967220</v>
+        <v>297707</v>
       </c>
       <c r="AB4" t="n">
-        <v>131218</v>
+        <v>20751</v>
       </c>
       <c r="AC4" t="n">
-        <v>272837</v>
+        <v>63338</v>
       </c>
       <c r="AD4" t="n">
-        <v>38702</v>
+        <v>10758</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>7133433</v>
+        <v>1237110</v>
       </c>
       <c r="AG4" t="n">
-        <v>8713937</v>
+        <v>1437940</v>
       </c>
       <c r="AH4" t="n">
-        <v>3383089</v>
+        <v>541446</v>
       </c>
       <c r="AI4" t="n">
-        <v>523090</v>
+        <v>72769</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1537969</v>
+        <v>262955</v>
       </c>
       <c r="AK4" t="n">
-        <v>465155</v>
+        <v>84863</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8433576822280884</v>
+        <v>0.7566365003585815</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6937711238861084</v>
+        <v>0.5446341037750244</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5922278761863708</v>
+        <v>0.4127046763896942</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3415253460407257</v>
+        <v>0.1757305264472961</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6626420617103577</v>
+        <v>0.4809899032115936</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7322689294815063</v>
+        <v>0.5602805018424988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>889</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>260105</v>
+        <v>69320</v>
       </c>
       <c r="E5" t="n">
-        <v>1779493</v>
+        <v>301948</v>
       </c>
       <c r="F5" t="n">
-        <v>5488348</v>
+        <v>412992</v>
       </c>
       <c r="G5" t="n">
-        <v>122044</v>
+        <v>17638</v>
       </c>
       <c r="H5" t="n">
-        <v>657174</v>
+        <v>116050</v>
       </c>
       <c r="I5" t="n">
-        <v>79872</v>
+        <v>19827</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5615615</v>
+        <v>1073086</v>
       </c>
       <c r="L5" t="n">
-        <v>7511219</v>
+        <v>1427262</v>
       </c>
       <c r="M5" t="n">
-        <v>2899577</v>
+        <v>525003</v>
       </c>
       <c r="N5" t="n">
-        <v>493432</v>
+        <v>72583</v>
       </c>
       <c r="O5" t="n">
-        <v>1288146</v>
+        <v>248592</v>
       </c>
       <c r="P5" t="n">
-        <v>382254</v>
+        <v>78119</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999629855155945</v>
+        <v>0.9999224543571472</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9204190373420715</v>
+        <v>0.8614943623542786</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8970852494239807</v>
+        <v>0.8258267045021057</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9597873091697693</v>
+        <v>0.9349327087402344</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9942343831062317</v>
+        <v>0.9920749068260193</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9822609424591064</v>
+        <v>0.9692421555519104</v>
       </c>
       <c r="W5" t="n">
-        <v>0.994714617729187</v>
+        <v>0.9903013706207275</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>345425</v>
+        <v>84782</v>
       </c>
       <c r="Z5" t="n">
-        <v>2064740</v>
+        <v>307141</v>
       </c>
       <c r="AA5" t="n">
-        <v>4951883</v>
+        <v>384662</v>
       </c>
       <c r="AB5" t="n">
-        <v>147089</v>
+        <v>18568</v>
       </c>
       <c r="AC5" t="n">
-        <v>776981</v>
+        <v>120446</v>
       </c>
       <c r="AD5" t="n">
-        <v>101807</v>
+        <v>22396</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>6724816</v>
+        <v>1143419</v>
       </c>
       <c r="AG5" t="n">
-        <v>9050413</v>
+        <v>1515394</v>
       </c>
       <c r="AH5" t="n">
-        <v>3436042</v>
+        <v>553333</v>
       </c>
       <c r="AI5" t="n">
-        <v>526967</v>
+        <v>73660</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1551839</v>
+        <v>265991</v>
       </c>
       <c r="AK5" t="n">
-        <v>466596</v>
+        <v>85286</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9041837453842163</v>
+        <v>0.8518686890602112</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8771768808364868</v>
+        <v>0.8162252306938171</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9528523683547974</v>
+        <v>0.9318760633468628</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9927398562431335</v>
+        <v>0.9908882975578308</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9786369800567627</v>
+        <v>0.9670857191085815</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.993557870388031</v>
+        <v>0.989412248134613</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1253</v>
+        <v>235</v>
       </c>
       <c r="D6" t="n">
-        <v>99286</v>
+        <v>16486</v>
       </c>
       <c r="E6" t="n">
-        <v>125231</v>
+        <v>21474</v>
       </c>
       <c r="F6" t="n">
-        <v>164574</v>
+        <v>18855</v>
       </c>
       <c r="G6" t="n">
-        <v>305847</v>
+        <v>16686</v>
       </c>
       <c r="H6" t="n">
-        <v>88333</v>
+        <v>12689</v>
       </c>
       <c r="I6" t="n">
-        <v>14755</v>
+        <v>2844</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>117158</v>
+        <v>17511</v>
       </c>
       <c r="Z6" t="n">
-        <v>138809</v>
+        <v>22123</v>
       </c>
       <c r="AA6" t="n">
-        <v>153173</v>
+        <v>18207</v>
       </c>
       <c r="AB6" t="n">
-        <v>272312</v>
+        <v>15609</v>
       </c>
       <c r="AC6" t="n">
-        <v>100552</v>
+        <v>12788</v>
       </c>
       <c r="AD6" t="n">
-        <v>17275</v>
+        <v>3031</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>396</v>
+        <v>69</v>
       </c>
       <c r="D7" t="n">
-        <v>17549</v>
+        <v>7927</v>
       </c>
       <c r="E7" t="n">
-        <v>228513</v>
+        <v>61367</v>
       </c>
       <c r="F7" t="n">
-        <v>695400</v>
+        <v>122065</v>
       </c>
       <c r="G7" t="n">
-        <v>89794</v>
+        <v>11899</v>
       </c>
       <c r="H7" t="n">
-        <v>3298210</v>
+        <v>262498</v>
       </c>
       <c r="I7" t="n">
-        <v>256494</v>
+        <v>45265</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>29014</v>
+        <v>11275</v>
       </c>
       <c r="Z7" t="n">
-        <v>297777</v>
+        <v>70197</v>
       </c>
       <c r="AA7" t="n">
-        <v>820137</v>
+        <v>125709</v>
       </c>
       <c r="AB7" t="n">
-        <v>101514</v>
+        <v>11649</v>
       </c>
       <c r="AC7" t="n">
-        <v>3034517</v>
+        <v>245099</v>
       </c>
       <c r="AD7" t="n">
-        <v>303397</v>
+        <v>47161</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>595</v>
+        <v>240</v>
       </c>
       <c r="E8" t="n">
-        <v>20022</v>
+        <v>6894</v>
       </c>
       <c r="F8" t="n">
-        <v>46370</v>
+        <v>13132</v>
       </c>
       <c r="G8" t="n">
-        <v>10662</v>
+        <v>2519</v>
       </c>
       <c r="H8" t="n">
-        <v>304406</v>
+        <v>55304</v>
       </c>
       <c r="I8" t="n">
-        <v>1358554</v>
+        <v>115567</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1400</v>
+        <v>702</v>
       </c>
       <c r="Z8" t="n">
-        <v>28236</v>
+        <v>8418</v>
       </c>
       <c r="AA8" t="n">
-        <v>62116</v>
+        <v>15806</v>
       </c>
       <c r="AB8" t="n">
-        <v>13586</v>
+        <v>2814</v>
       </c>
       <c r="AC8" t="n">
-        <v>361258</v>
+        <v>57546</v>
       </c>
       <c r="AD8" t="n">
-        <v>1274212</v>
+        <v>108400</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
